--- a/artfynd/A 64717-2023 artfynd.xlsx
+++ b/artfynd/A 64717-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118109625</v>
+        <v>118109629</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317480</v>
+        <v>317567</v>
       </c>
       <c r="R2" t="n">
-        <v>6546679</v>
+        <v>6546621</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Äldre exemplar på asplåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,19 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118109628</v>
+        <v>118109622</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317485</v>
+        <v>317482</v>
       </c>
       <c r="R3" t="n">
-        <v>6546642</v>
+        <v>6546666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,16 +882,11 @@
         <v>118109623</v>
       </c>
       <c r="B4" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -996,19 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118109622</v>
+        <v>118109625</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317482</v>
+        <v>317480</v>
       </c>
       <c r="R5" t="n">
-        <v>6546666</v>
+        <v>6546679</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118109629</v>
+        <v>118109628</v>
       </c>
       <c r="B6" t="n">
-        <v>90488</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317567</v>
+        <v>317485</v>
       </c>
       <c r="R6" t="n">
-        <v>6546621</v>
+        <v>6546642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre exemplar på asplåga</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 64717-2023 artfynd.xlsx
+++ b/artfynd/A 64717-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118109629</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118109622</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118109623</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118109625</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118109628</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>